--- a/business_forms/043_hair_consultation_request_form--business_forms.xlsx
+++ b/business_forms/043_hair_consultation_request_form--business_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -801,7 +801,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Submit</t>
+          <t>Submit2</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -824,7 +824,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Submit</t>
+          <t>Submit3</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -847,7 +847,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Submit</t>
+          <t>Submit4</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -870,7 +870,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Submit</t>
+          <t>Submit5</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -893,7 +893,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Submit</t>
+          <t>Submit6</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -916,7 +916,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Submit</t>
+          <t>Submit7</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -939,7 +939,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Submit</t>
+          <t>Submit8</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -962,7 +962,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Submit</t>
+          <t>Submit9</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -985,7 +985,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Submit</t>
+          <t>Submit10</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Submit</t>
+          <t>Submit11</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1031,7 +1031,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Submit</t>
+          <t>Submit12</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1054,7 +1054,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Submit</t>
+          <t>Submit13</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1077,7 +1077,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Submit</t>
+          <t>Submit14</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'blonde'}</t>
+          <t>blonde</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Blonde'}</t>
+          <t>Blonde</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'brown'}</t>
+          <t>brown</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Brown'}</t>
+          <t>Brown</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'red'}</t>
+          <t>red</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Red'}</t>
+          <t>Red</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'dandruff'}</t>
+          <t>dandruff</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Dandruff'}</t>
+          <t>Dandruff</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'dryness'}</t>
+          <t>dryness</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Dryness'}</t>
+          <t>Dryness</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'oilyness'}</t>
+          <t>oilyness</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Oilyness'}</t>
+          <t>Oilyness</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'haircut'}</t>
+          <t>haircut</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Haircut'}</t>
+          <t>Haircut</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'color'}</t>
+          <t>color</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Color'}</t>
+          <t>Color</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'style'}</t>
+          <t>style</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Style'}</t>
+          <t>Style</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'red'}</t>
+          <t>red</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Red'}</t>
+          <t>Red</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'brown'}</t>
+          <t>brown</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Brown'}</t>
+          <t>Brown</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'blonde'}</t>
+          <t>blonde</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Blonde'}</t>
+          <t>Blonde</t>
         </is>
       </c>
     </row>
